--- a/data/visits/Visits_2026-09-21.xlsx
+++ b/data/visits/Visits_2026-09-21.xlsx
@@ -436,16 +436,16 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
@@ -577,20 +577,16 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
+      <c r="C2" t="n">
+        <v>3645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Kashan</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>114723</t>
-        </is>
+      <c r="E2" t="n">
+        <v>114723</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -599,7 +595,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-21 09:07:43</t>
+          <t>2026-09-21 9:07:43</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -611,23 +607,47 @@
       <c r="J2" t="n">
         <v>100</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-21 09:40:52</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>24.945828</v>
+      </c>
+      <c r="M2" t="n">
+        <v>67.14618710000001</v>
+      </c>
+      <c r="N2" t="n">
+        <v>135.6000061035156</v>
+      </c>
+      <c r="O2" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Some Difference</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>00:33:09</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0.5525</v>
+      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T2" t="n">
         <v>9249.4</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>9224</v>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>Mismatch &gt; 1.5 km</t>

--- a/data/visits/Visits_2026-09-21.xlsx
+++ b/data/visits/Visits_2026-09-21.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -435,7 +435,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -443,7 +443,7 @@
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -609,7 +609,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-21 09:40:52</t>
+          <t>2026-09-21 9:40:52</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -619,7 +619,7 @@
         <v>67.14618710000001</v>
       </c>
       <c r="N2" t="n">
-        <v>135.6000061035156</v>
+        <v>135.6000061</v>
       </c>
       <c r="O2" t="n">
         <v>126.8</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>00:33:09</t>
+          <t>0:33:09</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -654,8 +654,96 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VIS-20260921094356-397E4A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3645</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101652</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AMMAR PETROLEUM SERVICES</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-21 9:43:56</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>24.9458035</v>
+      </c>
+      <c r="I3" t="n">
+        <v>67.14619620000001</v>
+      </c>
+      <c r="J3" t="n">
+        <v>149.6000061</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:38</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>24.83702</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67.0336494</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12.78600025177002</v>
+      </c>
+      <c r="O3" t="n">
+        <v>16588.8</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Big Difference</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>03:50:42</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>3.845</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>505.1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>16693.5</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V2"/>
+  <autoFilter ref="A1:V3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-21.xlsx
+++ b/data/visits/Visits_2026-09-21.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -435,15 +435,15 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -707,7 +707,7 @@
         <v>67.0336494</v>
       </c>
       <c r="N3" t="n">
-        <v>12.78600025177002</v>
+        <v>12.78600025</v>
       </c>
       <c r="O3" t="n">
         <v>16588.8</v>
@@ -719,7 +719,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>03:50:42</t>
+          <t>3:50:42</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -742,8 +742,76 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VIS-20260921144305-306C2D</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>116674</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PSO S/S -03 (CLIFF PETROLEUM SERVIC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:43:05</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>24.83707056322191</v>
+      </c>
+      <c r="I4" t="n">
+        <v>67.03360189724023</v>
+      </c>
+      <c r="J4" t="n">
+        <v>99</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V3"/>
+  <autoFilter ref="A1:V4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>